--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2981,53 +2981,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>91131356</v>
+        <v>128236820</v>
       </c>
       <c r="B21" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92635</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gärdesån_Ö3-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440072.1259368877</v>
+        <v>440053</v>
       </c>
       <c r="R21" t="n">
-        <v>7047690.816028876</v>
+        <v>7048358</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3051,22 +3046,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3077,81 +3062,64 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Möjlig kalktallskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>97079510</v>
+        <v>128236780</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92048</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440090.3191733454</v>
+        <v>440077</v>
       </c>
       <c r="R22" t="n">
-        <v>7047637.410037745</v>
+        <v>7048326</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3175,22 +3143,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3199,34 +3157,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>97079525</v>
+        <v>128236809</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3234,40 +3186,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439925.1195299322</v>
+        <v>440012</v>
       </c>
       <c r="R23" t="n">
-        <v>7047803.28115989</v>
+        <v>7047901</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3291,22 +3240,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3315,72 +3254,66 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>90799394</v>
+        <v>128236815</v>
       </c>
       <c r="B24" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91369</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440152.7779370788</v>
+        <v>439995</v>
       </c>
       <c r="R24" t="n">
-        <v>7048203.829398069</v>
+        <v>7047917</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3404,22 +3337,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3430,45 +3353,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Sälgar (flera)</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>90799392</v>
+        <v>128236803</v>
       </c>
       <c r="B25" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98802</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3476,37 +3380,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>219880</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440152.7779370788</v>
+        <v>440092</v>
       </c>
       <c r="R25" t="n">
-        <v>7048203.829398069</v>
+        <v>7048259</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3530,22 +3434,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3556,83 +3450,64 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Sälgar (flera)</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>90799468</v>
+        <v>128236819</v>
       </c>
       <c r="B26" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92659</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>4368</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440635.7918206314</v>
+        <v>440091</v>
       </c>
       <c r="R26" t="n">
-        <v>7047294.066192875</v>
+        <v>7048246</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3656,22 +3531,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3682,45 +3547,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>90799458</v>
+        <v>128236800</v>
       </c>
       <c r="B27" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3728,37 +3574,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440422.1981492973</v>
+        <v>440015</v>
       </c>
       <c r="R27" t="n">
-        <v>7047763.160909561</v>
+        <v>7048070</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3782,27 +3628,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3813,50 +3649,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Äldre sälg</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>90799473</v>
+        <v>128236797</v>
       </c>
       <c r="B28" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3864,37 +3676,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440583.1423300812</v>
+        <v>439930</v>
       </c>
       <c r="R28" t="n">
-        <v>7047415.901642947</v>
+        <v>7047883</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3918,22 +3730,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3944,88 +3751,64 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Äldre sälg</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>90799470</v>
+        <v>128236795</v>
       </c>
       <c r="B29" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440583.1423300812</v>
+        <v>439915</v>
       </c>
       <c r="R29" t="n">
-        <v>7047415.901642947</v>
+        <v>7047878</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4049,22 +3832,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4075,50 +3853,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Äldre sälg</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>90799389</v>
+        <v>128236811</v>
       </c>
       <c r="B30" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4126,37 +3880,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440152.7779370788</v>
+        <v>439940</v>
       </c>
       <c r="R30" t="n">
-        <v>7048203.829398069</v>
+        <v>7047955</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4180,22 +3934,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4206,45 +3950,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Sälgar (flera)</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>90799475</v>
+        <v>128236812</v>
       </c>
       <c r="B31" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91369</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4252,37 +3977,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440583.1423300812</v>
+        <v>440108</v>
       </c>
       <c r="R31" t="n">
-        <v>7047415.901642947</v>
+        <v>7048183</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4306,22 +4031,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4332,88 +4047,64 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Äldre sälg</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>90799460</v>
+        <v>128236816</v>
       </c>
       <c r="B32" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91369</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440422.1981492973</v>
+        <v>439928</v>
       </c>
       <c r="R32" t="n">
-        <v>7047763.160909561</v>
+        <v>7047874</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4437,27 +4128,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4468,88 +4144,60 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Äldre sälg</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>90799390</v>
+        <v>128236818</v>
       </c>
       <c r="B33" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90849</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>5734</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440152.7779370788</v>
+        <v>440038</v>
       </c>
       <c r="R33" t="n">
-        <v>7048203.829398069</v>
+        <v>7048412</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4573,22 +4221,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4597,85 +4235,67 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Sälgar (flera)</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>90799381</v>
+        <v>128236798</v>
       </c>
       <c r="B34" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440158.7940279006</v>
+        <v>440008</v>
       </c>
       <c r="R34" t="n">
-        <v>7048143.973987693</v>
+        <v>7048019</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4699,27 +4319,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Synobs av tjäder</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4730,78 +4340,64 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>91131405</v>
+        <v>128236779</v>
       </c>
       <c r="B35" t="n">
-        <v>95572</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88623</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221063</v>
+        <v>4412</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440564.9014531093</v>
+        <v>439849</v>
       </c>
       <c r="R35" t="n">
-        <v>7047323.931540202</v>
+        <v>7048382</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4825,22 +4421,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4851,83 +4437,64 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>91131390</v>
+        <v>128236799</v>
       </c>
       <c r="B36" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440283.885905911</v>
+        <v>440022</v>
       </c>
       <c r="R36" t="n">
-        <v>7047388.061842606</v>
+        <v>7048062</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4951,22 +4518,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4977,83 +4539,64 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>91131382</v>
+        <v>128236796</v>
       </c>
       <c r="B37" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57672</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222412</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440283.885905911</v>
+        <v>439918</v>
       </c>
       <c r="R37" t="n">
-        <v>7047388.061842606</v>
+        <v>7047885</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5077,22 +4620,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5103,40 +4641,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>91131398</v>
+        <v>91131356</v>
       </c>
       <c r="B38" t="n">
-        <v>96660</v>
+        <v>98520</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5149,34 +4673,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärdesån_Ö3-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440465.1222640315</v>
+        <v>440072.1259368877</v>
       </c>
       <c r="R38" t="n">
-        <v>7047361.028223578</v>
+        <v>7047690.816028876</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5203,7 +4727,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -5213,7 +4737,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5232,12 +4756,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS38" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
+          <t>Möjlig kalktallskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5259,10 +4778,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>91131389</v>
+        <v>97079510</v>
       </c>
       <c r="B39" t="n">
-        <v>96232</v>
+        <v>77506</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5271,38 +4790,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219795</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440283.885905911</v>
+        <v>440090.3191733454</v>
       </c>
       <c r="R39" t="n">
-        <v>7047388.061842606</v>
+        <v>7047637.410037745</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5329,7 +4851,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -5339,7 +4861,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5353,18 +4875,9 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5374,21 +4887,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>91131396</v>
+        <v>97079525</v>
       </c>
       <c r="B40" t="n">
-        <v>101680</v>
+        <v>77506</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5397,38 +4906,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440465.1222640315</v>
+        <v>439925.1195299322</v>
       </c>
       <c r="R40" t="n">
-        <v>7047361.028223578</v>
+        <v>7047803.28115989</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5455,7 +4967,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -5465,7 +4977,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5479,18 +4991,9 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5500,64 +5003,55 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>91131408</v>
+        <v>128236805</v>
       </c>
       <c r="B41" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440564.9014531093</v>
+        <v>440069</v>
       </c>
       <c r="R41" t="n">
-        <v>7047323.931540202</v>
+        <v>7047632</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5581,22 +5075,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5607,83 +5091,64 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>91131401</v>
+        <v>128236791</v>
       </c>
       <c r="B42" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440465.1222640315</v>
+        <v>439922</v>
       </c>
       <c r="R42" t="n">
-        <v>7047361.028223578</v>
+        <v>7047845</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5707,22 +5172,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5733,83 +5193,64 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>91131407</v>
+        <v>128236792</v>
       </c>
       <c r="B43" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440564.9014531093</v>
+        <v>439926</v>
       </c>
       <c r="R43" t="n">
-        <v>7047323.931540202</v>
+        <v>7047844</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5833,22 +5274,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5859,86 +5295,64 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>97079043</v>
+        <v>128236783</v>
       </c>
       <c r="B44" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440025.2851282395</v>
+        <v>440150</v>
       </c>
       <c r="R44" t="n">
-        <v>7048663.178585364</v>
+        <v>7047992</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5962,22 +5376,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5986,34 +5395,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>97079272</v>
+        <v>128236790</v>
       </c>
       <c r="B45" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6039,23 +5442,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440214.4427480109</v>
+        <v>439938</v>
       </c>
       <c r="R45" t="n">
-        <v>7048159.422972785</v>
+        <v>7047820</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6079,27 +5478,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6114,27 +5503,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>97079293</v>
+        <v>128236808</v>
       </c>
       <c r="B46" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6142,40 +5526,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440341.3908818047</v>
+        <v>440068</v>
       </c>
       <c r="R46" t="n">
-        <v>7047930.09822528</v>
+        <v>7047806</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6199,22 +5580,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6223,34 +5594,28 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>97079052</v>
+        <v>128236806</v>
       </c>
       <c r="B47" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6258,40 +5623,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439993.8154374501</v>
+        <v>440074</v>
       </c>
       <c r="R47" t="n">
-        <v>7048627.665063544</v>
+        <v>7047804</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6315,22 +5677,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6339,29 +5691,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>97079295</v>
+        <v>90799394</v>
       </c>
       <c r="B48" t="n">
-        <v>77506</v>
+        <v>78602</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6370,20 +5721,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6392,19 +5743,16 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440341.3908818047</v>
+        <v>440152.7779370788</v>
       </c>
       <c r="R48" t="n">
-        <v>7047930.09822528</v>
+        <v>7048203.829398069</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6431,7 +5779,7 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -6441,7 +5789,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -6449,20 +5797,24 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Sälgar (flera)</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6472,10 +5824,3941 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>90799392</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78603</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>440152.7779370788</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7048203.829398069</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Sälgar (flera)</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY48" t="inlineStr"/>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>90799468</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98520</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>440635.7918206314</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7047294.066192875</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>90799458</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78569</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>440422.1981492973</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7047763.160909561</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Äldre sälg</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>90799473</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78569</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>440583.1423300812</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7047415.901642947</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Äldre sälg</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>90799470</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78596</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>440583.1423300812</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7047415.901642947</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Äldre sälg</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>90799389</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78569</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>440152.7779370788</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7048203.829398069</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Sälgar (flera)</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>90799475</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78570</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>440583.1423300812</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7047415.901642947</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Äldre sälg</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>90799460</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78527</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>440422.1981492973</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7047763.160909561</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Äldre sälg</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>90799390</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78596</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>440152.7779370788</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7048203.829398069</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Sälgar (flera)</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>90799381</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98520</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>440158.7940279006</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7048143.973987693</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Synobs av tjäder</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>91131405</v>
+      </c>
+      <c r="B59" t="n">
+        <v>95572</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221063</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Trådfräken</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Equisetum scirpoides</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>440564.9014531093</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7047323.931540202</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>91131390</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98520</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>440283.885905911</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7047388.061842606</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>91131382</v>
+      </c>
+      <c r="B61" t="n">
+        <v>101680</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>440283.885905911</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7047388.061842606</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>91131398</v>
+      </c>
+      <c r="B62" t="n">
+        <v>96660</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>440465.1222640315</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7047361.028223578</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>91131389</v>
+      </c>
+      <c r="B63" t="n">
+        <v>96232</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>440283.885905911</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7047388.061842606</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>91131396</v>
+      </c>
+      <c r="B64" t="n">
+        <v>101680</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>440465.1222640315</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7047361.028223578</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>91131408</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98520</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>440564.9014531093</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7047323.931540202</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>91131401</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98520</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>440465.1222640315</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7047361.028223578</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>91131407</v>
+      </c>
+      <c r="B67" t="n">
+        <v>96660</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Gärde-Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>440564.9014531093</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7047323.931540202</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2019-07-16</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>97079043</v>
+      </c>
+      <c r="B68" t="n">
+        <v>90674</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus s.str.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Gärdesån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>440025.2851282395</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7048663.178585364</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>97079272</v>
+      </c>
+      <c r="B69" t="n">
+        <v>56395</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Gärdesån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>440214.4427480109</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7048159.422972785</v>
+      </c>
+      <c r="S69" t="n">
+        <v>25</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>97079293</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78569</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Gärdesån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>440341.3908818047</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7047930.09822528</v>
+      </c>
+      <c r="S70" t="n">
+        <v>25</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>97079052</v>
+      </c>
+      <c r="B71" t="n">
+        <v>77506</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Gärdesån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>439993.8154374501</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7048627.665063544</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>97079295</v>
+      </c>
+      <c r="B72" t="n">
+        <v>77506</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Gärdesån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>440341.3908818047</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7047930.09822528</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128236786</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Gärde S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>440548</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7047339</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128236784</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Gärde S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>440471</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7047318</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128236817</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Gärde S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>440606</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7047293</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128236814</v>
+      </c>
+      <c r="B76" t="n">
+        <v>91369</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Gärde S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>440566</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7047307</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128236789</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Gärde S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>440467</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7047649</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128236782</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Gärde S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>440231</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7048069</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128236785</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Gärde S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>440476</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7047442</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128236813</v>
+      </c>
+      <c r="B80" t="n">
+        <v>91369</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Gärde S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>440489</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7047346</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128236788</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Gärde S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>440530</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7047514</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -2984,7 +2984,7 @@
         <v>128236820</v>
       </c>
       <c r="B21" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>128236780</v>
       </c>
       <c r="B22" t="n">
-        <v>92048</v>
+        <v>92049</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128236809</v>
       </c>
       <c r="B23" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>128236815</v>
       </c>
       <c r="B24" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>128236803</v>
       </c>
       <c r="B25" t="n">
-        <v>98802</v>
+        <v>98803</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>128236819</v>
       </c>
       <c r="B26" t="n">
-        <v>92659</v>
+        <v>92660</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128236800</v>
+        <v>128236797</v>
       </c>
       <c r="B27" t="n">
         <v>57672</v>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440015</v>
+        <v>439930</v>
       </c>
       <c r="R27" t="n">
-        <v>7048070</v>
+        <v>7047883</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3665,7 +3665,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128236797</v>
+        <v>128236800</v>
       </c>
       <c r="B28" t="n">
         <v>57672</v>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439930</v>
+        <v>440015</v>
       </c>
       <c r="R28" t="n">
-        <v>7047883</v>
+        <v>7048070</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3872,7 +3872,7 @@
         <v>128236811</v>
       </c>
       <c r="B30" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>128236812</v>
       </c>
       <c r="B31" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>128236816</v>
       </c>
       <c r="B32" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>128236818</v>
       </c>
       <c r="B33" t="n">
-        <v>90849</v>
+        <v>90850</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4254,10 +4254,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128236798</v>
+        <v>128236779</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>88624</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4265,21 +4265,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440008</v>
+        <v>439849</v>
       </c>
       <c r="R34" t="n">
-        <v>7048019</v>
+        <v>7048382</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4325,11 +4325,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4356,10 +4351,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128236779</v>
+        <v>128236798</v>
       </c>
       <c r="B35" t="n">
-        <v>88623</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4367,21 +4362,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4391,10 +4386,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439849</v>
+        <v>440008</v>
       </c>
       <c r="R35" t="n">
-        <v>7048382</v>
+        <v>7048019</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4427,6 +4422,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4453,7 +4453,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128236799</v>
+        <v>128236796</v>
       </c>
       <c r="B36" t="n">
         <v>57672</v>
@@ -4488,10 +4488,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440022</v>
+        <v>439918</v>
       </c>
       <c r="R36" t="n">
-        <v>7048062</v>
+        <v>7047885</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4555,7 +4555,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128236796</v>
+        <v>128236799</v>
       </c>
       <c r="B37" t="n">
         <v>57672</v>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439918</v>
+        <v>440022</v>
       </c>
       <c r="R37" t="n">
-        <v>7047885</v>
+        <v>7048062</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5013,7 +5013,7 @@
         <v>128236805</v>
       </c>
       <c r="B41" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128236783</v>
+        <v>128236790</v>
       </c>
       <c r="B44" t="n">
         <v>57672</v>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440150</v>
+        <v>439938</v>
       </c>
       <c r="R44" t="n">
-        <v>7047992</v>
+        <v>7047820</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5413,7 +5413,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128236790</v>
+        <v>128236783</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>439938</v>
+        <v>440150</v>
       </c>
       <c r="R45" t="n">
-        <v>7047820</v>
+        <v>7047992</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5518,7 +5518,7 @@
         <v>128236808</v>
       </c>
       <c r="B46" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>128236806</v>
       </c>
       <c r="B47" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>128236814</v>
       </c>
       <c r="B76" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128236789</v>
+        <v>128236782</v>
       </c>
       <c r="B77" t="n">
         <v>57672</v>
@@ -9292,10 +9292,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440467</v>
+        <v>440231</v>
       </c>
       <c r="R77" t="n">
-        <v>7047649</v>
+        <v>7048069</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9359,7 +9359,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128236782</v>
+        <v>128236789</v>
       </c>
       <c r="B78" t="n">
         <v>57672</v>
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440231</v>
+        <v>440467</v>
       </c>
       <c r="R78" t="n">
-        <v>7048069</v>
+        <v>7047649</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9566,7 +9566,7 @@
         <v>128236813</v>
       </c>
       <c r="B80" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -3563,7 +3563,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128236797</v>
+        <v>128236800</v>
       </c>
       <c r="B27" t="n">
         <v>57672</v>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439930</v>
+        <v>440015</v>
       </c>
       <c r="R27" t="n">
-        <v>7047883</v>
+        <v>7048070</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3665,7 +3665,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128236800</v>
+        <v>128236797</v>
       </c>
       <c r="B28" t="n">
         <v>57672</v>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440015</v>
+        <v>439930</v>
       </c>
       <c r="R28" t="n">
-        <v>7048070</v>
+        <v>7047883</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128236811</v>
+        <v>128236812</v>
       </c>
       <c r="B30" t="n">
-        <v>91348</v>
+        <v>91370</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439940</v>
+        <v>440108</v>
       </c>
       <c r="R30" t="n">
-        <v>7047955</v>
+        <v>7048183</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128236812</v>
+        <v>128236816</v>
       </c>
       <c r="B31" t="n">
         <v>91370</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440108</v>
+        <v>439928</v>
       </c>
       <c r="R31" t="n">
-        <v>7048183</v>
+        <v>7047874</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4063,10 +4063,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128236816</v>
+        <v>128236811</v>
       </c>
       <c r="B32" t="n">
-        <v>91370</v>
+        <v>91348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,21 +4074,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439928</v>
+        <v>439940</v>
       </c>
       <c r="R32" t="n">
-        <v>7047874</v>
+        <v>7047955</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4453,7 +4453,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128236796</v>
+        <v>128236799</v>
       </c>
       <c r="B36" t="n">
         <v>57672</v>
@@ -4488,10 +4488,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439918</v>
+        <v>440022</v>
       </c>
       <c r="R36" t="n">
-        <v>7047885</v>
+        <v>7048062</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4555,7 +4555,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128236799</v>
+        <v>128236796</v>
       </c>
       <c r="B37" t="n">
         <v>57672</v>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440022</v>
+        <v>439918</v>
       </c>
       <c r="R37" t="n">
-        <v>7048062</v>
+        <v>7047885</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5311,7 +5311,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128236790</v>
+        <v>128236783</v>
       </c>
       <c r="B44" t="n">
         <v>57672</v>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439938</v>
+        <v>440150</v>
       </c>
       <c r="R44" t="n">
-        <v>7047820</v>
+        <v>7047992</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5413,7 +5413,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128236783</v>
+        <v>128236790</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440150</v>
+        <v>439938</v>
       </c>
       <c r="R45" t="n">
-        <v>7047992</v>
+        <v>7047820</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -9257,7 +9257,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128236782</v>
+        <v>128236789</v>
       </c>
       <c r="B77" t="n">
         <v>57672</v>
@@ -9292,10 +9292,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440231</v>
+        <v>440467</v>
       </c>
       <c r="R77" t="n">
-        <v>7048069</v>
+        <v>7047649</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9359,7 +9359,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128236789</v>
+        <v>128236782</v>
       </c>
       <c r="B78" t="n">
         <v>57672</v>
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440467</v>
+        <v>440231</v>
       </c>
       <c r="R78" t="n">
-        <v>7047649</v>
+        <v>7048069</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -2984,7 +2984,7 @@
         <v>128236820</v>
       </c>
       <c r="B21" t="n">
-        <v>92636</v>
+        <v>92644</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>128236780</v>
       </c>
       <c r="B22" t="n">
-        <v>92049</v>
+        <v>92057</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128236809</v>
       </c>
       <c r="B23" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>128236815</v>
       </c>
       <c r="B24" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>128236803</v>
       </c>
       <c r="B25" t="n">
-        <v>98803</v>
+        <v>98811</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>128236819</v>
       </c>
       <c r="B26" t="n">
-        <v>92660</v>
+        <v>92668</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3563,10 +3563,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128236800</v>
+        <v>128236797</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440015</v>
+        <v>439930</v>
       </c>
       <c r="R27" t="n">
-        <v>7048070</v>
+        <v>7047883</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128236797</v>
+        <v>128236800</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439930</v>
+        <v>440015</v>
       </c>
       <c r="R28" t="n">
-        <v>7047883</v>
+        <v>7048070</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3770,7 +3770,7 @@
         <v>128236795</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128236812</v>
+        <v>128236811</v>
       </c>
       <c r="B30" t="n">
-        <v>91370</v>
+        <v>91356</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440108</v>
+        <v>439940</v>
       </c>
       <c r="R30" t="n">
-        <v>7048183</v>
+        <v>7047955</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3969,7 +3969,7 @@
         <v>128236816</v>
       </c>
       <c r="B31" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4063,10 +4063,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128236811</v>
+        <v>128236812</v>
       </c>
       <c r="B32" t="n">
-        <v>91348</v>
+        <v>91378</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,21 +4074,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439940</v>
+        <v>440108</v>
       </c>
       <c r="R32" t="n">
-        <v>7047955</v>
+        <v>7048183</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4163,7 +4163,7 @@
         <v>128236818</v>
       </c>
       <c r="B33" t="n">
-        <v>90850</v>
+        <v>90856</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>128236779</v>
       </c>
       <c r="B34" t="n">
-        <v>88624</v>
+        <v>88630</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>128236798</v>
       </c>
       <c r="B35" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4453,10 +4453,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128236799</v>
+        <v>128236796</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4488,10 +4488,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440022</v>
+        <v>439918</v>
       </c>
       <c r="R36" t="n">
-        <v>7048062</v>
+        <v>7047885</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4555,10 +4555,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128236796</v>
+        <v>128236799</v>
       </c>
       <c r="B37" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439918</v>
+        <v>440022</v>
       </c>
       <c r="R37" t="n">
-        <v>7047885</v>
+        <v>7048062</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5013,7 +5013,7 @@
         <v>128236805</v>
       </c>
       <c r="B41" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>128236791</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>128236792</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5311,10 +5311,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128236783</v>
+        <v>128236790</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440150</v>
+        <v>439938</v>
       </c>
       <c r="R44" t="n">
-        <v>7047992</v>
+        <v>7047820</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5413,10 +5413,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128236790</v>
+        <v>128236783</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>439938</v>
+        <v>440150</v>
       </c>
       <c r="R45" t="n">
-        <v>7047820</v>
+        <v>7047992</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5518,7 +5518,7 @@
         <v>128236808</v>
       </c>
       <c r="B46" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>128236806</v>
       </c>
       <c r="B47" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>128236786</v>
       </c>
       <c r="B73" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>128236784</v>
       </c>
       <c r="B74" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>128236817</v>
       </c>
       <c r="B75" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>128236814</v>
       </c>
       <c r="B76" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9257,10 +9257,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128236789</v>
+        <v>128236782</v>
       </c>
       <c r="B77" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9292,10 +9292,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440467</v>
+        <v>440231</v>
       </c>
       <c r="R77" t="n">
-        <v>7047649</v>
+        <v>7048069</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9359,10 +9359,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128236782</v>
+        <v>128236789</v>
       </c>
       <c r="B78" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440231</v>
+        <v>440467</v>
       </c>
       <c r="R78" t="n">
-        <v>7048069</v>
+        <v>7047649</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9464,7 +9464,7 @@
         <v>128236785</v>
       </c>
       <c r="B79" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>128236813</v>
       </c>
       <c r="B80" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>128236788</v>
       </c>
       <c r="B81" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -2984,7 +2984,7 @@
         <v>128236820</v>
       </c>
       <c r="B21" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>128236780</v>
       </c>
       <c r="B22" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128236809</v>
       </c>
       <c r="B23" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>128236815</v>
       </c>
       <c r="B24" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>128236803</v>
       </c>
       <c r="B25" t="n">
-        <v>98811</v>
+        <v>98904</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>128236819</v>
       </c>
       <c r="B26" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3563,10 +3563,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128236797</v>
+        <v>128236800</v>
       </c>
       <c r="B27" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439930</v>
+        <v>440015</v>
       </c>
       <c r="R27" t="n">
-        <v>7047883</v>
+        <v>7048070</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128236800</v>
+        <v>128236795</v>
       </c>
       <c r="B28" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440015</v>
+        <v>439915</v>
       </c>
       <c r="R28" t="n">
-        <v>7048070</v>
+        <v>7047878</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3767,10 +3767,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128236795</v>
+        <v>128236797</v>
       </c>
       <c r="B29" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439915</v>
+        <v>439930</v>
       </c>
       <c r="R29" t="n">
-        <v>7047878</v>
+        <v>7047883</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3872,7 +3872,7 @@
         <v>128236811</v>
       </c>
       <c r="B30" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128236816</v>
+        <v>128236812</v>
       </c>
       <c r="B31" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439928</v>
+        <v>440108</v>
       </c>
       <c r="R31" t="n">
-        <v>7047874</v>
+        <v>7048183</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4063,10 +4063,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128236812</v>
+        <v>128236816</v>
       </c>
       <c r="B32" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440108</v>
+        <v>439928</v>
       </c>
       <c r="R32" t="n">
-        <v>7048183</v>
+        <v>7047874</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4163,7 +4163,7 @@
         <v>128236818</v>
       </c>
       <c r="B33" t="n">
-        <v>90856</v>
+        <v>90948</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>128236779</v>
       </c>
       <c r="B34" t="n">
-        <v>88630</v>
+        <v>88722</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>128236798</v>
       </c>
       <c r="B35" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4453,10 +4453,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128236796</v>
+        <v>128236799</v>
       </c>
       <c r="B36" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4488,10 +4488,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439918</v>
+        <v>440022</v>
       </c>
       <c r="R36" t="n">
-        <v>7047885</v>
+        <v>7048062</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4555,10 +4555,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128236799</v>
+        <v>128236796</v>
       </c>
       <c r="B37" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440022</v>
+        <v>439918</v>
       </c>
       <c r="R37" t="n">
-        <v>7048062</v>
+        <v>7047885</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5013,7 +5013,7 @@
         <v>128236805</v>
       </c>
       <c r="B41" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>128236791</v>
       </c>
       <c r="B42" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>128236792</v>
       </c>
       <c r="B43" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5311,10 +5311,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128236790</v>
+        <v>128236783</v>
       </c>
       <c r="B44" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439938</v>
+        <v>440150</v>
       </c>
       <c r="R44" t="n">
-        <v>7047820</v>
+        <v>7047992</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5413,10 +5413,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128236783</v>
+        <v>128236790</v>
       </c>
       <c r="B45" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440150</v>
+        <v>439938</v>
       </c>
       <c r="R45" t="n">
-        <v>7047992</v>
+        <v>7047820</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5518,7 +5518,7 @@
         <v>128236808</v>
       </c>
       <c r="B46" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>128236806</v>
       </c>
       <c r="B47" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>128236786</v>
       </c>
       <c r="B73" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>128236784</v>
       </c>
       <c r="B74" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>128236817</v>
       </c>
       <c r="B75" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>128236814</v>
       </c>
       <c r="B76" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9257,10 +9257,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128236782</v>
+        <v>128236789</v>
       </c>
       <c r="B77" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9292,10 +9292,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440231</v>
+        <v>440467</v>
       </c>
       <c r="R77" t="n">
-        <v>7048069</v>
+        <v>7047649</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9359,10 +9359,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128236789</v>
+        <v>128236782</v>
       </c>
       <c r="B78" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440467</v>
+        <v>440231</v>
       </c>
       <c r="R78" t="n">
-        <v>7047649</v>
+        <v>7048069</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9464,7 +9464,7 @@
         <v>128236785</v>
       </c>
       <c r="B79" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>128236813</v>
       </c>
       <c r="B80" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>128236788</v>
       </c>
       <c r="B81" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -3665,7 +3665,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128236795</v>
+        <v>128236797</v>
       </c>
       <c r="B28" t="n">
         <v>57685</v>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439915</v>
+        <v>439930</v>
       </c>
       <c r="R28" t="n">
-        <v>7047878</v>
+        <v>7047883</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3767,7 +3767,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128236797</v>
+        <v>128236795</v>
       </c>
       <c r="B29" t="n">
         <v>57685</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439930</v>
+        <v>439915</v>
       </c>
       <c r="R29" t="n">
-        <v>7047883</v>
+        <v>7047878</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3869,10 +3869,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128236811</v>
+        <v>128236816</v>
       </c>
       <c r="B30" t="n">
-        <v>91448</v>
+        <v>91470</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439940</v>
+        <v>439928</v>
       </c>
       <c r="R30" t="n">
-        <v>7047955</v>
+        <v>7047874</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4063,10 +4063,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128236816</v>
+        <v>128236811</v>
       </c>
       <c r="B32" t="n">
-        <v>91470</v>
+        <v>91448</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,21 +4074,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439928</v>
+        <v>439940</v>
       </c>
       <c r="R32" t="n">
-        <v>7047874</v>
+        <v>7047955</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -3869,10 +3869,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128236816</v>
+        <v>128236811</v>
       </c>
       <c r="B30" t="n">
-        <v>91470</v>
+        <v>91448</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439928</v>
+        <v>439940</v>
       </c>
       <c r="R30" t="n">
-        <v>7047874</v>
+        <v>7047955</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128236812</v>
+        <v>128236816</v>
       </c>
       <c r="B31" t="n">
         <v>91470</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440108</v>
+        <v>439928</v>
       </c>
       <c r="R31" t="n">
-        <v>7048183</v>
+        <v>7047874</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4063,10 +4063,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128236811</v>
+        <v>128236812</v>
       </c>
       <c r="B32" t="n">
-        <v>91448</v>
+        <v>91470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,21 +4074,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439940</v>
+        <v>440108</v>
       </c>
       <c r="R32" t="n">
-        <v>7047955</v>
+        <v>7048183</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4254,10 +4254,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128236779</v>
+        <v>128236798</v>
       </c>
       <c r="B34" t="n">
-        <v>88722</v>
+        <v>57685</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4265,21 +4265,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439849</v>
+        <v>440008</v>
       </c>
       <c r="R34" t="n">
-        <v>7048382</v>
+        <v>7048019</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4325,6 +4325,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4351,7 +4356,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128236798</v>
+        <v>128236799</v>
       </c>
       <c r="B35" t="n">
         <v>57685</v>
@@ -4386,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440008</v>
+        <v>440022</v>
       </c>
       <c r="R35" t="n">
-        <v>7048019</v>
+        <v>7048062</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4426,7 +4431,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4453,7 +4458,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128236799</v>
+        <v>128236796</v>
       </c>
       <c r="B36" t="n">
         <v>57685</v>
@@ -4488,10 +4493,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440022</v>
+        <v>439918</v>
       </c>
       <c r="R36" t="n">
-        <v>7048062</v>
+        <v>7047885</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4528,7 +4533,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4555,10 +4560,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128236796</v>
+        <v>128236779</v>
       </c>
       <c r="B37" t="n">
-        <v>57685</v>
+        <v>88722</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,21 +4571,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4590,10 +4595,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439918</v>
+        <v>439849</v>
       </c>
       <c r="R37" t="n">
-        <v>7047885</v>
+        <v>7048382</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4626,11 +4631,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -4254,10 +4254,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128236798</v>
+        <v>128236779</v>
       </c>
       <c r="B34" t="n">
-        <v>57685</v>
+        <v>88722</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4265,21 +4265,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440008</v>
+        <v>439849</v>
       </c>
       <c r="R34" t="n">
-        <v>7048019</v>
+        <v>7048382</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4325,11 +4325,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4356,7 +4351,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128236799</v>
+        <v>128236798</v>
       </c>
       <c r="B35" t="n">
         <v>57685</v>
@@ -4391,10 +4386,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440022</v>
+        <v>440008</v>
       </c>
       <c r="R35" t="n">
-        <v>7048062</v>
+        <v>7048019</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4431,7 +4426,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4458,7 +4453,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128236796</v>
+        <v>128236799</v>
       </c>
       <c r="B36" t="n">
         <v>57685</v>
@@ -4493,10 +4488,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439918</v>
+        <v>440022</v>
       </c>
       <c r="R36" t="n">
-        <v>7047885</v>
+        <v>7048062</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4533,7 +4528,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4560,10 +4555,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128236779</v>
+        <v>128236796</v>
       </c>
       <c r="B37" t="n">
-        <v>88722</v>
+        <v>57685</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4571,21 +4566,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4595,10 +4590,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439849</v>
+        <v>439918</v>
       </c>
       <c r="R37" t="n">
-        <v>7048382</v>
+        <v>7047885</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4631,6 +4626,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -2984,7 +2984,7 @@
         <v>128236820</v>
       </c>
       <c r="B21" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>128236780</v>
       </c>
       <c r="B22" t="n">
-        <v>92149</v>
+        <v>92161</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128236809</v>
       </c>
       <c r="B23" t="n">
-        <v>91448</v>
+        <v>91460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>128236815</v>
       </c>
       <c r="B24" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>128236803</v>
       </c>
       <c r="B25" t="n">
-        <v>98904</v>
+        <v>98918</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>128236819</v>
       </c>
       <c r="B26" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>128236800</v>
       </c>
       <c r="B27" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>128236797</v>
       </c>
       <c r="B28" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>128236795</v>
       </c>
       <c r="B29" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128236811</v>
+        <v>128236816</v>
       </c>
       <c r="B30" t="n">
-        <v>91448</v>
+        <v>91482</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439940</v>
+        <v>439928</v>
       </c>
       <c r="R30" t="n">
-        <v>7047955</v>
+        <v>7047874</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128236816</v>
+        <v>128236812</v>
       </c>
       <c r="B31" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439928</v>
+        <v>440108</v>
       </c>
       <c r="R31" t="n">
-        <v>7047874</v>
+        <v>7048183</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4063,10 +4063,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128236812</v>
+        <v>128236811</v>
       </c>
       <c r="B32" t="n">
-        <v>91470</v>
+        <v>91460</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,21 +4074,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440108</v>
+        <v>439940</v>
       </c>
       <c r="R32" t="n">
-        <v>7048183</v>
+        <v>7047955</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4163,7 +4163,7 @@
         <v>128236818</v>
       </c>
       <c r="B33" t="n">
-        <v>90948</v>
+        <v>90960</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4254,10 +4254,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128236779</v>
+        <v>128236798</v>
       </c>
       <c r="B34" t="n">
-        <v>88722</v>
+        <v>57689</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4265,21 +4265,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439849</v>
+        <v>440008</v>
       </c>
       <c r="R34" t="n">
-        <v>7048382</v>
+        <v>7048019</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4325,6 +4325,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4351,10 +4356,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128236798</v>
+        <v>128236799</v>
       </c>
       <c r="B35" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4386,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440008</v>
+        <v>440022</v>
       </c>
       <c r="R35" t="n">
-        <v>7048019</v>
+        <v>7048062</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4426,7 +4431,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4453,10 +4458,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128236799</v>
+        <v>128236796</v>
       </c>
       <c r="B36" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4488,10 +4493,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440022</v>
+        <v>439918</v>
       </c>
       <c r="R36" t="n">
-        <v>7048062</v>
+        <v>7047885</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4528,7 +4533,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4555,10 +4560,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128236796</v>
+        <v>128236779</v>
       </c>
       <c r="B37" t="n">
-        <v>57685</v>
+        <v>88734</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,21 +4571,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4590,10 +4595,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439918</v>
+        <v>439849</v>
       </c>
       <c r="R37" t="n">
-        <v>7047885</v>
+        <v>7048382</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4626,11 +4631,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5013,7 +5013,7 @@
         <v>128236805</v>
       </c>
       <c r="B41" t="n">
-        <v>91448</v>
+        <v>91460</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>128236791</v>
       </c>
       <c r="B42" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>128236792</v>
       </c>
       <c r="B43" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>128236783</v>
       </c>
       <c r="B44" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>128236790</v>
       </c>
       <c r="B45" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>128236808</v>
       </c>
       <c r="B46" t="n">
-        <v>91448</v>
+        <v>91460</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>128236806</v>
       </c>
       <c r="B47" t="n">
-        <v>91448</v>
+        <v>91460</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>128236786</v>
       </c>
       <c r="B73" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>128236784</v>
       </c>
       <c r="B74" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>128236817</v>
       </c>
       <c r="B75" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>128236814</v>
       </c>
       <c r="B76" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>128236789</v>
       </c>
       <c r="B77" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>128236782</v>
       </c>
       <c r="B78" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>128236785</v>
       </c>
       <c r="B79" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>128236813</v>
       </c>
       <c r="B80" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>128236788</v>
       </c>
       <c r="B81" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -2984,7 +2984,7 @@
         <v>128236820</v>
       </c>
       <c r="B21" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>128236780</v>
       </c>
       <c r="B22" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128236809</v>
       </c>
       <c r="B23" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>128236815</v>
       </c>
       <c r="B24" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>128236803</v>
       </c>
       <c r="B25" t="n">
-        <v>98918</v>
+        <v>98921</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>128236819</v>
       </c>
       <c r="B26" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128236816</v>
+        <v>128236812</v>
       </c>
       <c r="B30" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439928</v>
+        <v>440108</v>
       </c>
       <c r="R30" t="n">
-        <v>7047874</v>
+        <v>7048183</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128236812</v>
+        <v>128236816</v>
       </c>
       <c r="B31" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440108</v>
+        <v>439928</v>
       </c>
       <c r="R31" t="n">
-        <v>7048183</v>
+        <v>7047874</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4066,7 +4066,7 @@
         <v>128236811</v>
       </c>
       <c r="B32" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>128236818</v>
       </c>
       <c r="B33" t="n">
-        <v>90960</v>
+        <v>90962</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4254,10 +4254,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128236798</v>
+        <v>128236779</v>
       </c>
       <c r="B34" t="n">
-        <v>57689</v>
+        <v>88736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4265,21 +4265,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440008</v>
+        <v>439849</v>
       </c>
       <c r="R34" t="n">
-        <v>7048019</v>
+        <v>7048382</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4325,11 +4325,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4356,7 +4351,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128236799</v>
+        <v>128236798</v>
       </c>
       <c r="B35" t="n">
         <v>57689</v>
@@ -4391,10 +4386,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440022</v>
+        <v>440008</v>
       </c>
       <c r="R35" t="n">
-        <v>7048062</v>
+        <v>7048019</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4431,7 +4426,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4458,7 +4453,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128236796</v>
+        <v>128236799</v>
       </c>
       <c r="B36" t="n">
         <v>57689</v>
@@ -4493,10 +4488,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439918</v>
+        <v>440022</v>
       </c>
       <c r="R36" t="n">
-        <v>7047885</v>
+        <v>7048062</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4533,7 +4528,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4560,10 +4555,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128236779</v>
+        <v>128236796</v>
       </c>
       <c r="B37" t="n">
-        <v>88734</v>
+        <v>57689</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4571,21 +4566,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4595,10 +4590,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439849</v>
+        <v>439918</v>
       </c>
       <c r="R37" t="n">
-        <v>7048382</v>
+        <v>7047885</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4631,6 +4626,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5013,7 +5013,7 @@
         <v>128236805</v>
       </c>
       <c r="B41" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>128236808</v>
       </c>
       <c r="B46" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>128236806</v>
       </c>
       <c r="B47" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>128236817</v>
       </c>
       <c r="B75" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>128236814</v>
       </c>
       <c r="B76" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>128236813</v>
       </c>
       <c r="B80" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -3372,7 +3372,7 @@
         <v>128236803</v>
       </c>
       <c r="B25" t="n">
-        <v>98921</v>
+        <v>98925</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128236812</v>
+        <v>128236811</v>
       </c>
       <c r="B30" t="n">
-        <v>91484</v>
+        <v>91462</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440108</v>
+        <v>439940</v>
       </c>
       <c r="R30" t="n">
-        <v>7048183</v>
+        <v>7047955</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128236816</v>
+        <v>128236812</v>
       </c>
       <c r="B31" t="n">
         <v>91484</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439928</v>
+        <v>440108</v>
       </c>
       <c r="R31" t="n">
-        <v>7047874</v>
+        <v>7048183</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4063,10 +4063,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128236811</v>
+        <v>128236816</v>
       </c>
       <c r="B32" t="n">
-        <v>91462</v>
+        <v>91484</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,21 +4074,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439940</v>
+        <v>439928</v>
       </c>
       <c r="R32" t="n">
-        <v>7047955</v>
+        <v>7047874</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -2984,7 +2984,7 @@
         <v>128236820</v>
       </c>
       <c r="B21" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>128236780</v>
       </c>
       <c r="B22" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128236809</v>
       </c>
       <c r="B23" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>128236815</v>
       </c>
       <c r="B24" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>128236803</v>
       </c>
       <c r="B25" t="n">
-        <v>98925</v>
+        <v>98926</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>128236819</v>
       </c>
       <c r="B26" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>128236811</v>
       </c>
       <c r="B30" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>128236812</v>
       </c>
       <c r="B31" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>128236816</v>
       </c>
       <c r="B32" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>128236818</v>
       </c>
       <c r="B33" t="n">
-        <v>90962</v>
+        <v>90963</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>128236805</v>
       </c>
       <c r="B41" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>128236808</v>
       </c>
       <c r="B46" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>128236806</v>
       </c>
       <c r="B47" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>128236814</v>
       </c>
       <c r="B76" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>128236813</v>
       </c>
       <c r="B80" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -3869,10 +3869,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128236811</v>
+        <v>128236812</v>
       </c>
       <c r="B30" t="n">
-        <v>91463</v>
+        <v>91485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439940</v>
+        <v>440108</v>
       </c>
       <c r="R30" t="n">
-        <v>7047955</v>
+        <v>7048183</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128236812</v>
+        <v>128236816</v>
       </c>
       <c r="B31" t="n">
         <v>91485</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440108</v>
+        <v>439928</v>
       </c>
       <c r="R31" t="n">
-        <v>7048183</v>
+        <v>7047874</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4063,10 +4063,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128236816</v>
+        <v>128236811</v>
       </c>
       <c r="B32" t="n">
-        <v>91485</v>
+        <v>91463</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,21 +4074,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439928</v>
+        <v>439940</v>
       </c>
       <c r="R32" t="n">
-        <v>7047874</v>
+        <v>7047955</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -2984,7 +2984,7 @@
         <v>128236820</v>
       </c>
       <c r="B21" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>128236780</v>
       </c>
       <c r="B22" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128236809</v>
       </c>
       <c r="B23" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>128236815</v>
       </c>
       <c r="B24" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>128236803</v>
       </c>
       <c r="B25" t="n">
-        <v>98926</v>
+        <v>98953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>128236819</v>
       </c>
       <c r="B26" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>128236800</v>
       </c>
       <c r="B27" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>128236797</v>
       </c>
       <c r="B28" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>128236795</v>
       </c>
       <c r="B29" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128236812</v>
+        <v>128236811</v>
       </c>
       <c r="B30" t="n">
-        <v>91485</v>
+        <v>91490</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440108</v>
+        <v>439940</v>
       </c>
       <c r="R30" t="n">
-        <v>7048183</v>
+        <v>7047955</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128236816</v>
+        <v>128236812</v>
       </c>
       <c r="B31" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439928</v>
+        <v>440108</v>
       </c>
       <c r="R31" t="n">
-        <v>7047874</v>
+        <v>7048183</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4063,10 +4063,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128236811</v>
+        <v>128236816</v>
       </c>
       <c r="B32" t="n">
-        <v>91463</v>
+        <v>91512</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,21 +4074,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439940</v>
+        <v>439928</v>
       </c>
       <c r="R32" t="n">
-        <v>7047955</v>
+        <v>7047874</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4163,7 +4163,7 @@
         <v>128236818</v>
       </c>
       <c r="B33" t="n">
-        <v>90963</v>
+        <v>90990</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4254,10 +4254,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128236779</v>
+        <v>128236798</v>
       </c>
       <c r="B34" t="n">
-        <v>88736</v>
+        <v>57716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4265,21 +4265,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439849</v>
+        <v>440008</v>
       </c>
       <c r="R34" t="n">
-        <v>7048382</v>
+        <v>7048019</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4325,6 +4325,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4351,10 +4356,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128236798</v>
+        <v>128236799</v>
       </c>
       <c r="B35" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4386,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440008</v>
+        <v>440022</v>
       </c>
       <c r="R35" t="n">
-        <v>7048019</v>
+        <v>7048062</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4426,7 +4431,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4453,10 +4458,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128236799</v>
+        <v>128236796</v>
       </c>
       <c r="B36" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4488,10 +4493,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440022</v>
+        <v>439918</v>
       </c>
       <c r="R36" t="n">
-        <v>7048062</v>
+        <v>7047885</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4528,7 +4533,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4555,10 +4560,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128236796</v>
+        <v>128236779</v>
       </c>
       <c r="B37" t="n">
-        <v>57689</v>
+        <v>88763</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,21 +4571,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4590,10 +4595,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439918</v>
+        <v>439849</v>
       </c>
       <c r="R37" t="n">
-        <v>7047885</v>
+        <v>7048382</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4626,11 +4631,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5013,7 +5013,7 @@
         <v>128236805</v>
       </c>
       <c r="B41" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>128236791</v>
       </c>
       <c r="B42" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>128236792</v>
       </c>
       <c r="B43" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>128236783</v>
       </c>
       <c r="B44" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>128236790</v>
       </c>
       <c r="B45" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>128236808</v>
       </c>
       <c r="B46" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>128236806</v>
       </c>
       <c r="B47" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>128236786</v>
       </c>
       <c r="B73" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>128236784</v>
       </c>
       <c r="B74" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>128236817</v>
       </c>
       <c r="B75" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>128236814</v>
       </c>
       <c r="B76" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>128236789</v>
       </c>
       <c r="B77" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>128236782</v>
       </c>
       <c r="B78" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>128236785</v>
       </c>
       <c r="B79" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>128236813</v>
       </c>
       <c r="B80" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>128236788</v>
       </c>
       <c r="B81" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -3563,7 +3563,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128236800</v>
+        <v>128236797</v>
       </c>
       <c r="B27" t="n">
         <v>57716</v>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440015</v>
+        <v>439930</v>
       </c>
       <c r="R27" t="n">
-        <v>7048070</v>
+        <v>7047883</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3665,7 +3665,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128236797</v>
+        <v>128236800</v>
       </c>
       <c r="B28" t="n">
         <v>57716</v>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439930</v>
+        <v>440015</v>
       </c>
       <c r="R28" t="n">
-        <v>7047883</v>
+        <v>7048070</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128236811</v>
+        <v>128236816</v>
       </c>
       <c r="B30" t="n">
-        <v>91490</v>
+        <v>91512</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3880,21 +3880,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439940</v>
+        <v>439928</v>
       </c>
       <c r="R30" t="n">
-        <v>7047955</v>
+        <v>7047874</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4063,10 +4063,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128236816</v>
+        <v>128236811</v>
       </c>
       <c r="B32" t="n">
-        <v>91512</v>
+        <v>91490</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,21 +4074,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439928</v>
+        <v>439940</v>
       </c>
       <c r="R32" t="n">
-        <v>7047874</v>
+        <v>7047955</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4254,10 +4254,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128236798</v>
+        <v>128236779</v>
       </c>
       <c r="B34" t="n">
-        <v>57716</v>
+        <v>88763</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4265,21 +4265,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440008</v>
+        <v>439849</v>
       </c>
       <c r="R34" t="n">
-        <v>7048019</v>
+        <v>7048382</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4325,11 +4325,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4356,7 +4351,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128236799</v>
+        <v>128236798</v>
       </c>
       <c r="B35" t="n">
         <v>57716</v>
@@ -4391,10 +4386,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440022</v>
+        <v>440008</v>
       </c>
       <c r="R35" t="n">
-        <v>7048062</v>
+        <v>7048019</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4431,7 +4426,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4560,10 +4555,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128236779</v>
+        <v>128236799</v>
       </c>
       <c r="B37" t="n">
-        <v>88763</v>
+        <v>57716</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4571,21 +4566,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4412</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4595,10 +4590,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439849</v>
+        <v>440022</v>
       </c>
       <c r="R37" t="n">
-        <v>7048382</v>
+        <v>7048062</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4631,6 +4626,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5311,7 +5311,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128236783</v>
+        <v>128236790</v>
       </c>
       <c r="B44" t="n">
         <v>57716</v>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440150</v>
+        <v>439938</v>
       </c>
       <c r="R44" t="n">
-        <v>7047992</v>
+        <v>7047820</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5413,7 +5413,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128236790</v>
+        <v>128236783</v>
       </c>
       <c r="B45" t="n">
         <v>57716</v>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>439938</v>
+        <v>440150</v>
       </c>
       <c r="R45" t="n">
-        <v>7047820</v>
+        <v>7047992</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -9257,7 +9257,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128236789</v>
+        <v>128236782</v>
       </c>
       <c r="B77" t="n">
         <v>57716</v>
@@ -9292,10 +9292,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440467</v>
+        <v>440231</v>
       </c>
       <c r="R77" t="n">
-        <v>7047649</v>
+        <v>7048069</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9359,7 +9359,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128236782</v>
+        <v>128236789</v>
       </c>
       <c r="B78" t="n">
         <v>57716</v>
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440231</v>
+        <v>440467</v>
       </c>
       <c r="R78" t="n">
-        <v>7048069</v>
+        <v>7047649</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -2984,7 +2984,7 @@
         <v>128236820</v>
       </c>
       <c r="B21" t="n">
-        <v>92778</v>
+        <v>92788</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>128236780</v>
       </c>
       <c r="B22" t="n">
-        <v>92191</v>
+        <v>92201</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>128236809</v>
       </c>
       <c r="B23" t="n">
-        <v>91490</v>
+        <v>91500</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>128236815</v>
       </c>
       <c r="B24" t="n">
-        <v>91512</v>
+        <v>91522</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>128236803</v>
       </c>
       <c r="B25" t="n">
-        <v>98953</v>
+        <v>98966</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>128236819</v>
       </c>
       <c r="B26" t="n">
-        <v>92802</v>
+        <v>92812</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128236797</v>
+        <v>128236800</v>
       </c>
       <c r="B27" t="n">
         <v>57716</v>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439930</v>
+        <v>440015</v>
       </c>
       <c r="R27" t="n">
-        <v>7047883</v>
+        <v>7048070</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3665,7 +3665,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128236800</v>
+        <v>128236797</v>
       </c>
       <c r="B28" t="n">
         <v>57716</v>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440015</v>
+        <v>439930</v>
       </c>
       <c r="R28" t="n">
-        <v>7048070</v>
+        <v>7047883</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128236816</v>
+        <v>128236812</v>
       </c>
       <c r="B30" t="n">
-        <v>91512</v>
+        <v>91522</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439928</v>
+        <v>440108</v>
       </c>
       <c r="R30" t="n">
-        <v>7047874</v>
+        <v>7048183</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128236812</v>
+        <v>128236816</v>
       </c>
       <c r="B31" t="n">
-        <v>91512</v>
+        <v>91522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440108</v>
+        <v>439928</v>
       </c>
       <c r="R31" t="n">
-        <v>7048183</v>
+        <v>7047874</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4066,7 +4066,7 @@
         <v>128236811</v>
       </c>
       <c r="B32" t="n">
-        <v>91490</v>
+        <v>91500</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>128236818</v>
       </c>
       <c r="B33" t="n">
-        <v>90990</v>
+        <v>91000</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>128236779</v>
       </c>
       <c r="B34" t="n">
-        <v>88763</v>
+        <v>88768</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128236796</v>
+        <v>128236799</v>
       </c>
       <c r="B36" t="n">
         <v>57716</v>
@@ -4488,10 +4488,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439918</v>
+        <v>440022</v>
       </c>
       <c r="R36" t="n">
-        <v>7047885</v>
+        <v>7048062</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4555,7 +4555,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128236799</v>
+        <v>128236796</v>
       </c>
       <c r="B37" t="n">
         <v>57716</v>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440022</v>
+        <v>439918</v>
       </c>
       <c r="R37" t="n">
-        <v>7048062</v>
+        <v>7047885</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5013,7 +5013,7 @@
         <v>128236805</v>
       </c>
       <c r="B41" t="n">
-        <v>91490</v>
+        <v>91500</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128236790</v>
+        <v>128236783</v>
       </c>
       <c r="B44" t="n">
         <v>57716</v>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439938</v>
+        <v>440150</v>
       </c>
       <c r="R44" t="n">
-        <v>7047820</v>
+        <v>7047992</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5413,7 +5413,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128236783</v>
+        <v>128236790</v>
       </c>
       <c r="B45" t="n">
         <v>57716</v>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440150</v>
+        <v>439938</v>
       </c>
       <c r="R45" t="n">
-        <v>7047992</v>
+        <v>7047820</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5518,7 +5518,7 @@
         <v>128236808</v>
       </c>
       <c r="B46" t="n">
-        <v>91490</v>
+        <v>91500</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>128236806</v>
       </c>
       <c r="B47" t="n">
-        <v>91490</v>
+        <v>91500</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>128236817</v>
       </c>
       <c r="B75" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>128236814</v>
       </c>
       <c r="B76" t="n">
-        <v>91512</v>
+        <v>91522</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128236782</v>
+        <v>128236789</v>
       </c>
       <c r="B77" t="n">
         <v>57716</v>
@@ -9292,10 +9292,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440231</v>
+        <v>440467</v>
       </c>
       <c r="R77" t="n">
-        <v>7048069</v>
+        <v>7047649</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9359,7 +9359,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128236789</v>
+        <v>128236782</v>
       </c>
       <c r="B78" t="n">
         <v>57716</v>
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440467</v>
+        <v>440231</v>
       </c>
       <c r="R78" t="n">
-        <v>7047649</v>
+        <v>7048069</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9566,7 +9566,7 @@
         <v>128236813</v>
       </c>
       <c r="B80" t="n">
-        <v>91512</v>
+        <v>91522</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -675,49 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90799376</v>
+        <v>128236809</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440087.1038034639</v>
+        <v>440012</v>
       </c>
       <c r="R2" t="n">
-        <v>7048509.110149929</v>
+        <v>7047901</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,45 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90799374</v>
+        <v>128236811</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440119.8455742975</v>
+        <v>439940</v>
       </c>
       <c r="R3" t="n">
-        <v>7048375.199019565</v>
+        <v>7047955</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,27 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,80 +853,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91131365</v>
+        <v>97079531</v>
       </c>
       <c r="B4" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gärdesån-Tångeråsen, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440034.0967388083</v>
+        <v>440019</v>
       </c>
       <c r="R4" t="n">
-        <v>7047876.132423092</v>
+        <v>7048078</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,22 +937,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,13 +951,9 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Möjlig kalktallskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1038,26 +963,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91131267</v>
+        <v>128236780</v>
       </c>
       <c r="B5" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,37 +981,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219795</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440002.021403469</v>
+        <v>440077</v>
       </c>
       <c r="R5" t="n">
-        <v>7048282.016218459</v>
+        <v>7048326</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,22 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,69 +1055,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91131309</v>
+        <v>128236820</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440102.1312412921</v>
+        <v>440053</v>
       </c>
       <c r="R6" t="n">
-        <v>7048359.037805371</v>
+        <v>7048358</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,22 +1132,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,83 +1148,64 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91131311</v>
+        <v>128236819</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>4368</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440076.1376786886</v>
+        <v>440091</v>
       </c>
       <c r="R7" t="n">
-        <v>7048400.987937612</v>
+        <v>7048246</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,22 +1229,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,83 +1245,64 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91131314</v>
+        <v>128236779</v>
       </c>
       <c r="B8" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219880</v>
+        <v>4412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440087.1038034639</v>
+        <v>439849</v>
       </c>
       <c r="R8" t="n">
-        <v>7048509.110149929</v>
+        <v>7048382</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1487,22 +1326,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,80 +1342,64 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>91131308</v>
+        <v>97079078</v>
       </c>
       <c r="B9" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219880</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440102.1312412921</v>
+        <v>440038</v>
       </c>
       <c r="R9" t="n">
-        <v>7048359.037805371</v>
+        <v>7048312</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1613,22 +1426,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1637,18 +1440,9 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1658,61 +1452,55 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>91131313</v>
+        <v>97079538</v>
       </c>
       <c r="B10" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440087.1038034639</v>
+        <v>440015</v>
       </c>
       <c r="R10" t="n">
-        <v>7048509.110149929</v>
+        <v>7048165</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1739,22 +1527,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1763,18 +1541,9 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1784,61 +1553,55 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>91131373</v>
+        <v>97079058</v>
       </c>
       <c r="B11" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gärdesån-Tångeråsen, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440012.9505090829</v>
+        <v>439984</v>
       </c>
       <c r="R11" t="n">
-        <v>7047914.876748392</v>
+        <v>7048506</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1865,22 +1628,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1889,13 +1642,9 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Möjlig kalktallskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1905,61 +1654,55 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>91131370</v>
+        <v>97079535</v>
       </c>
       <c r="B12" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gärdesån-Tångeråsen, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440012.9505090829</v>
+        <v>440008</v>
       </c>
       <c r="R12" t="n">
-        <v>7047914.876748392</v>
+        <v>7048146</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1986,22 +1729,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2010,13 +1743,9 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Möjlig kalktallskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2026,48 +1755,39 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>91131315</v>
+        <v>90799374</v>
       </c>
       <c r="B13" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2077,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440087.1038034639</v>
+        <v>440120</v>
       </c>
       <c r="R13" t="n">
-        <v>7048509.110149929</v>
+        <v>7048375</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2110,19 +1830,14 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2163,53 +1878,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>91131372</v>
+        <v>128236793</v>
       </c>
       <c r="B14" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219795</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gärdesån-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440012.9505090829</v>
+        <v>439901</v>
       </c>
       <c r="R14" t="n">
-        <v>7047914.876748392</v>
+        <v>7047874</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2233,22 +1943,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2259,78 +1964,64 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Möjlig kalktallskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>91131268</v>
+        <v>128236794</v>
       </c>
       <c r="B15" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440002.021403469</v>
+        <v>439899</v>
       </c>
       <c r="R15" t="n">
-        <v>7048282.016218459</v>
+        <v>7047901</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2354,22 +2045,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2384,31 +2070,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97079531</v>
+        <v>128236795</v>
       </c>
       <c r="B16" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2416,40 +2093,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440019.6072900151</v>
+        <v>439915</v>
       </c>
       <c r="R16" t="n">
-        <v>7048078.382703119</v>
+        <v>7047878</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2473,22 +2147,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2497,75 +2166,66 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97079538</v>
+        <v>128236796</v>
       </c>
       <c r="B17" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440014.5445481038</v>
+        <v>439918</v>
       </c>
       <c r="R17" t="n">
-        <v>7048164.972177582</v>
+        <v>7047885</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2589,22 +2249,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2613,34 +2268,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97079058</v>
+        <v>128236797</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2648,40 +2297,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439984.3873293845</v>
+        <v>439930</v>
       </c>
       <c r="R18" t="n">
-        <v>7048506.59010612</v>
+        <v>7047883</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2705,22 +2351,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2729,76 +2370,66 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97079546</v>
+        <v>128236798</v>
       </c>
       <c r="B19" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440022.0886006004</v>
+        <v>440008</v>
       </c>
       <c r="R19" t="n">
-        <v>7048186.230028968</v>
+        <v>7048019</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2822,22 +2453,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2846,34 +2472,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>97079535</v>
+        <v>128236799</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2881,40 +2501,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440007.935010805</v>
+        <v>440022</v>
       </c>
       <c r="R20" t="n">
-        <v>7048145.925771126</v>
+        <v>7048062</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2938,22 +2555,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2962,29 +2574,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128236820</v>
+        <v>128236800</v>
       </c>
       <c r="B21" t="n">
-        <v>92788</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,21 +2603,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3016,10 +2627,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440053</v>
+        <v>440015</v>
       </c>
       <c r="R21" t="n">
-        <v>7048358</v>
+        <v>7048070</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3052,6 +2663,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3078,10 +2694,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128236780</v>
+        <v>91131267</v>
       </c>
       <c r="B22" t="n">
-        <v>92201</v>
+        <v>99017</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3089,37 +2705,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>219795</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440077</v>
+        <v>440002</v>
       </c>
       <c r="R22" t="n">
-        <v>7048326</v>
+        <v>7048282</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3143,12 +2759,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3163,60 +2779,64 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128236809</v>
+        <v>91131372</v>
       </c>
       <c r="B23" t="n">
-        <v>91500</v>
+        <v>99017</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>219795</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärdesån-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440012</v>
+        <v>440013</v>
       </c>
       <c r="R23" t="n">
-        <v>7047901</v>
+        <v>7047915</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3240,12 +2860,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3256,64 +2876,73 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Möjlig kalktallskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128236815</v>
+        <v>91131313</v>
       </c>
       <c r="B24" t="n">
-        <v>91522</v>
+        <v>99142</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439995</v>
+        <v>440087</v>
       </c>
       <c r="R24" t="n">
-        <v>7047917</v>
+        <v>7048509</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3337,12 +2966,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3353,26 +2982,40 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128236803</v>
+        <v>91131365</v>
       </c>
       <c r="B25" t="n">
-        <v>98966</v>
+        <v>99142</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3380,37 +3023,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219880</v>
+        <v>219847</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärdesån-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440092</v>
+        <v>440034</v>
       </c>
       <c r="R25" t="n">
-        <v>7048259</v>
+        <v>7047876</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3434,12 +3077,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3450,64 +3093,73 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Möjlig kalktallskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128236819</v>
+        <v>91131308</v>
       </c>
       <c r="B26" t="n">
-        <v>92812</v>
+        <v>99456</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4368</v>
+        <v>219880</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440091</v>
+        <v>440102</v>
       </c>
       <c r="R26" t="n">
-        <v>7048246</v>
+        <v>7048359</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3531,12 +3183,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3547,64 +3199,78 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128236800</v>
+        <v>91131314</v>
       </c>
       <c r="B27" t="n">
-        <v>57716</v>
+        <v>99456</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440015</v>
+        <v>440087</v>
       </c>
       <c r="R27" t="n">
-        <v>7048070</v>
+        <v>7048509</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3628,17 +3294,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3649,48 +3310,62 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128236797</v>
+        <v>128236803</v>
       </c>
       <c r="B28" t="n">
-        <v>57716</v>
+        <v>99456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3700,10 +3375,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439930</v>
+        <v>440092</v>
       </c>
       <c r="R28" t="n">
-        <v>7047883</v>
+        <v>7048259</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3736,11 +3411,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3767,48 +3437,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128236795</v>
+        <v>91131370</v>
       </c>
       <c r="B29" t="n">
-        <v>57716</v>
+        <v>104628</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>222412</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärdesån-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439915</v>
+        <v>440013</v>
       </c>
       <c r="R29" t="n">
-        <v>7047878</v>
+        <v>7047915</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3832,17 +3502,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3853,64 +3518,73 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Möjlig kalktallskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128236812</v>
+        <v>91131268</v>
       </c>
       <c r="B30" t="n">
-        <v>91522</v>
+        <v>101326</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440108</v>
+        <v>440002</v>
       </c>
       <c r="R30" t="n">
-        <v>7048183</v>
+        <v>7048282</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3934,12 +3608,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3954,60 +3628,64 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128236816</v>
+        <v>91131309</v>
       </c>
       <c r="B31" t="n">
-        <v>91522</v>
+        <v>101326</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439928</v>
+        <v>440102</v>
       </c>
       <c r="R31" t="n">
-        <v>7047874</v>
+        <v>7048359</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4031,12 +3709,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4047,64 +3725,78 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128236811</v>
+        <v>91131311</v>
       </c>
       <c r="B32" t="n">
-        <v>91500</v>
+        <v>101326</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439940</v>
+        <v>440076</v>
       </c>
       <c r="R32" t="n">
-        <v>7047955</v>
+        <v>7048401</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4128,12 +3820,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4144,60 +3836,78 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128236818</v>
+        <v>91131315</v>
       </c>
       <c r="B33" t="n">
-        <v>91000</v>
+        <v>101326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5734</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440038</v>
+        <v>440087</v>
       </c>
       <c r="R33" t="n">
-        <v>7048412</v>
+        <v>7048509</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4221,12 +3931,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4235,67 +3945,80 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128236779</v>
+        <v>91131373</v>
       </c>
       <c r="B34" t="n">
-        <v>88768</v>
+        <v>101326</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4412</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärdesån-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439849</v>
+        <v>440013</v>
       </c>
       <c r="R34" t="n">
-        <v>7048382</v>
+        <v>7047915</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4319,12 +4042,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4335,64 +4058,77 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Möjlig kalktallskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128236798</v>
+        <v>97079546</v>
       </c>
       <c r="B35" t="n">
-        <v>57716</v>
+        <v>101326</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440008</v>
+        <v>440022</v>
       </c>
       <c r="R35" t="n">
-        <v>7048019</v>
+        <v>7048186</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4416,17 +4152,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4435,66 +4166,63 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128236799</v>
+        <v>90799376</v>
       </c>
       <c r="B36" t="n">
-        <v>57716</v>
+        <v>99038</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>223597</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440022</v>
+        <v>440087</v>
       </c>
       <c r="R36" t="n">
-        <v>7048062</v>
+        <v>7048509</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4518,17 +4246,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4539,26 +4262,40 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128236796</v>
+        <v>128236805</v>
       </c>
       <c r="B37" t="n">
-        <v>57716</v>
+        <v>91905</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,21 +4303,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4590,10 +4327,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439918</v>
+        <v>440069</v>
       </c>
       <c r="R37" t="n">
-        <v>7047885</v>
+        <v>7047632</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4626,11 +4363,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4657,53 +4389,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>91131356</v>
+        <v>128236806</v>
       </c>
       <c r="B38" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gärdesån_Ö3-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440072.1259368877</v>
+        <v>440074</v>
       </c>
       <c r="R38" t="n">
-        <v>7047690.816028876</v>
+        <v>7047804</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4727,22 +4454,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4753,40 +4470,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Möjlig kalktallskog</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>97079510</v>
+        <v>128236808</v>
       </c>
       <c r="B39" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4794,40 +4497,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440090.3191733454</v>
+        <v>440068</v>
       </c>
       <c r="R39" t="n">
-        <v>7047637.410037745</v>
+        <v>7047806</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4851,22 +4551,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4875,34 +4565,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>97079525</v>
+        <v>128236810</v>
       </c>
       <c r="B40" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4910,40 +4594,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439925.1195299322</v>
+        <v>439966</v>
       </c>
       <c r="R40" t="n">
-        <v>7047803.28115989</v>
+        <v>7047817</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4967,22 +4648,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4991,67 +4662,69 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128236805</v>
+        <v>97079510</v>
       </c>
       <c r="B41" t="n">
-        <v>91500</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440069</v>
+        <v>440090</v>
       </c>
       <c r="R41" t="n">
-        <v>7047632</v>
+        <v>7047637</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5075,12 +4748,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5089,66 +4762,70 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128236791</v>
+        <v>97079525</v>
       </c>
       <c r="B42" t="n">
-        <v>57716</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439922</v>
+        <v>439925</v>
       </c>
       <c r="R42" t="n">
-        <v>7047845</v>
+        <v>7047803</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5172,17 +4849,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5191,28 +4863,29 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128236792</v>
+        <v>128236783</v>
       </c>
       <c r="B43" t="n">
-        <v>57716</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5244,10 +4917,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>439926</v>
+        <v>440150</v>
       </c>
       <c r="R43" t="n">
-        <v>7047844</v>
+        <v>7047992</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5311,10 +4984,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128236783</v>
+        <v>128236790</v>
       </c>
       <c r="B44" t="n">
-        <v>57716</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5346,10 +5019,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440150</v>
+        <v>439938</v>
       </c>
       <c r="R44" t="n">
-        <v>7047992</v>
+        <v>7047820</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5413,10 +5086,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128236790</v>
+        <v>128236791</v>
       </c>
       <c r="B45" t="n">
-        <v>57716</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5448,10 +5121,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>439938</v>
+        <v>439922</v>
       </c>
       <c r="R45" t="n">
-        <v>7047820</v>
+        <v>7047845</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5515,10 +5188,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128236808</v>
+        <v>128236792</v>
       </c>
       <c r="B46" t="n">
-        <v>91500</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5526,21 +5199,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5550,10 +5223,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440068</v>
+        <v>439926</v>
       </c>
       <c r="R46" t="n">
-        <v>7047806</v>
+        <v>7047844</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5586,6 +5259,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5612,48 +5290,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128236806</v>
+        <v>91131356</v>
       </c>
       <c r="B47" t="n">
-        <v>91500</v>
+        <v>101326</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärdesån_Ö3-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440074</v>
+        <v>440072</v>
       </c>
       <c r="R47" t="n">
-        <v>7047804</v>
+        <v>7047691</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5677,12 +5355,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5693,31 +5371,35 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Möjlig kalktallskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>90799394</v>
+        <v>128236781</v>
       </c>
       <c r="B48" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5725,37 +5407,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>3298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440152.7779370788</v>
+        <v>440483</v>
       </c>
       <c r="R48" t="n">
-        <v>7048203.829398069</v>
+        <v>7047353</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5779,22 +5461,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5805,83 +5477,64 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Sälgar (flera)</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>90799392</v>
+        <v>128236817</v>
       </c>
       <c r="B49" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440152.7779370788</v>
+        <v>440606</v>
       </c>
       <c r="R49" t="n">
-        <v>7048203.829398069</v>
+        <v>7047293</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5905,22 +5558,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5931,83 +5579,64 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Sälgar (flera)</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>90799468</v>
+        <v>128236784</v>
       </c>
       <c r="B50" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440635.7918206314</v>
+        <v>440471</v>
       </c>
       <c r="R50" t="n">
-        <v>7047294.066192875</v>
+        <v>7047318</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6031,22 +5660,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6057,45 +5681,26 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>90799458</v>
+        <v>128236786</v>
       </c>
       <c r="B51" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6103,37 +5708,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440422.1981492973</v>
+        <v>440548</v>
       </c>
       <c r="R51" t="n">
-        <v>7047763.160909561</v>
+        <v>7047339</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6157,27 +5762,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6188,72 +5783,48 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Äldre sälg</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>90799473</v>
+        <v>91131407</v>
       </c>
       <c r="B52" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6263,10 +5834,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440583.1423300812</v>
+        <v>440565</v>
       </c>
       <c r="R52" t="n">
-        <v>7047415.901642947</v>
+        <v>7047324</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6296,21 +5867,11 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6323,11 +5884,6 @@
       <c r="AI52" t="inlineStr">
         <is>
           <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Äldre sälg</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
@@ -6354,15 +5910,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>90799470</v>
+        <v>91131405</v>
       </c>
       <c r="B53" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98030</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6370,21 +5921,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>221063</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6394,10 +5945,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440583.1423300812</v>
+        <v>440565</v>
       </c>
       <c r="R53" t="n">
-        <v>7047415.901642947</v>
+        <v>7047324</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6427,21 +5978,11 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6454,11 +5995,6 @@
       <c r="AI53" t="inlineStr">
         <is>
           <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Äldre sälg</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
@@ -6485,37 +6021,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>90799389</v>
+        <v>90799468</v>
       </c>
       <c r="B54" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6525,10 +6056,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440152.7779370788</v>
+        <v>440636</v>
       </c>
       <c r="R54" t="n">
-        <v>7048203.829398069</v>
+        <v>7047294</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6558,21 +6089,11 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6587,9 +6108,9 @@
           <t>Kalkbarrskog</t>
         </is>
       </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Sälgar (flera)</t>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6611,37 +6132,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>90799475</v>
+        <v>91131408</v>
       </c>
       <c r="B55" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6651,10 +6167,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440583.1423300812</v>
+        <v>440565</v>
       </c>
       <c r="R55" t="n">
-        <v>7047415.901642947</v>
+        <v>7047324</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6684,21 +6200,11 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6711,11 +6217,6 @@
       <c r="AI55" t="inlineStr">
         <is>
           <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Äldre sälg</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
@@ -6742,37 +6243,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>90799460</v>
+        <v>90799475</v>
       </c>
       <c r="B56" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6782,10 +6278,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440422.1981492973</v>
+        <v>440583</v>
       </c>
       <c r="R56" t="n">
-        <v>7047763.160909561</v>
+        <v>7047416</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6815,24 +6311,9 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6878,50 +6359,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>90799390</v>
+        <v>97079043</v>
       </c>
       <c r="B57" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440152.7779370788</v>
+        <v>440025</v>
       </c>
       <c r="R57" t="n">
-        <v>7048203.829398069</v>
+        <v>7048663</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6948,22 +6427,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6972,18 +6441,9 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Sälgar (flera)</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -6993,61 +6453,55 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>90799381</v>
+        <v>97079052</v>
       </c>
       <c r="B58" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440158.7940279006</v>
+        <v>439994</v>
       </c>
       <c r="R58" t="n">
-        <v>7048143.973987693</v>
+        <v>7048628</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7074,27 +6528,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Synobs av tjäder</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7103,13 +6542,9 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7119,61 +6554,55 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>91131405</v>
+        <v>97079295</v>
       </c>
       <c r="B59" t="n">
-        <v>95572</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440564.9014531093</v>
+        <v>440341</v>
       </c>
       <c r="R59" t="n">
-        <v>7047323.931540202</v>
+        <v>7047930</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7200,22 +6629,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7224,18 +6648,9 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7245,48 +6660,39 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>91131390</v>
+        <v>90799389</v>
       </c>
       <c r="B60" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7296,10 +6702,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440283.885905911</v>
+        <v>440153</v>
       </c>
       <c r="R60" t="n">
-        <v>7047388.061842606</v>
+        <v>7048204</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7329,21 +6735,11 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7358,9 +6754,9 @@
           <t>Kalkbarrskog</t>
         </is>
       </c>
-      <c r="AS60" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Sälgar (flera)</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7382,37 +6778,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>91131382</v>
+        <v>90799458</v>
       </c>
       <c r="B61" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7422,10 +6813,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440283.885905911</v>
+        <v>440422</v>
       </c>
       <c r="R61" t="n">
-        <v>7047388.061842606</v>
+        <v>7047763</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7455,19 +6846,14 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7482,6 +6868,11 @@
       <c r="AI61" t="inlineStr">
         <is>
           <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Äldre sälg</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
@@ -7508,37 +6899,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>91131398</v>
+        <v>90799473</v>
       </c>
       <c r="B62" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7548,10 +6934,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440465.1222640315</v>
+        <v>440583</v>
       </c>
       <c r="R62" t="n">
-        <v>7047361.028223578</v>
+        <v>7047416</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7581,21 +6967,11 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7608,6 +6984,11 @@
       <c r="AI62" t="inlineStr">
         <is>
           <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Äldre sälg</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
@@ -7634,50 +7015,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>91131389</v>
+        <v>97079293</v>
       </c>
       <c r="B63" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219795</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gärde-Tångeråsen, Jmt</t>
+          <t>Gärdesån, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440283.885905911</v>
+        <v>440341</v>
       </c>
       <c r="R63" t="n">
-        <v>7047388.061842606</v>
+        <v>7047930</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7704,22 +7083,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7728,18 +7097,9 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7749,26 +7109,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>91131396</v>
+        <v>90799390</v>
       </c>
       <c r="B64" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7776,21 +7127,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222412</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7800,10 +7151,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440465.1222640315</v>
+        <v>440153</v>
       </c>
       <c r="R64" t="n">
-        <v>7047361.028223578</v>
+        <v>7048204</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7833,21 +7184,11 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7862,9 +7203,9 @@
           <t>Kalkbarrskog</t>
         </is>
       </c>
-      <c r="AS64" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Sälgar (flera)</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7886,15 +7227,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>91131408</v>
+        <v>90799470</v>
       </c>
       <c r="B65" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7902,21 +7238,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7926,10 +7262,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440564.9014531093</v>
+        <v>440583</v>
       </c>
       <c r="R65" t="n">
-        <v>7047323.931540202</v>
+        <v>7047416</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7959,21 +7295,11 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7986,6 +7312,11 @@
       <c r="AI65" t="inlineStr">
         <is>
           <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Äldre sälg</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
@@ -8012,15 +7343,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>91131401</v>
+        <v>90799394</v>
       </c>
       <c r="B66" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8028,21 +7354,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8052,10 +7378,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440465.1222640315</v>
+        <v>440153</v>
       </c>
       <c r="R66" t="n">
-        <v>7047361.028223578</v>
+        <v>7048204</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8085,21 +7411,11 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8114,9 +7430,9 @@
           <t>Kalkbarrskog</t>
         </is>
       </c>
-      <c r="AS66" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Sälgar (flera)</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8138,15 +7454,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>91131407</v>
+        <v>90799392</v>
       </c>
       <c r="B67" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8154,21 +7465,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219880</v>
+        <v>6464</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8178,10 +7489,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440564.9014531093</v>
+        <v>440153</v>
       </c>
       <c r="R67" t="n">
-        <v>7047323.931540202</v>
+        <v>7048204</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8211,21 +7522,11 @@
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2019-07-16</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8240,9 +7541,9 @@
           <t>Kalkbarrskog</t>
         </is>
       </c>
-      <c r="AS67" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Sälgar (flera)</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8264,42 +7565,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>97079043</v>
+        <v>97079272</v>
       </c>
       <c r="B68" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8307,10 +7604,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440025.2851282395</v>
+        <v>440215</v>
       </c>
       <c r="R68" t="n">
-        <v>7048663.178585364</v>
+        <v>7048160</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8340,19 +7637,14 @@
           <t>2021-10-26</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2021-10-26</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8361,7 +7653,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8380,15 +7671,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>97079272</v>
+        <v>128236782</v>
       </c>
       <c r="B69" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8414,23 +7700,19 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440214.4427480109</v>
+        <v>440231</v>
       </c>
       <c r="R69" t="n">
-        <v>7048159.422972785</v>
+        <v>7048069</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8454,27 +7736,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8489,27 +7761,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>97079293</v>
+        <v>128236785</v>
       </c>
       <c r="B70" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8517,40 +7784,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440341.3908818047</v>
+        <v>440476</v>
       </c>
       <c r="R70" t="n">
-        <v>7047930.09822528</v>
+        <v>7047442</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8574,22 +7838,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8598,34 +7857,28 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>97079052</v>
+        <v>128236788</v>
       </c>
       <c r="B71" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8633,40 +7886,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>439993.8154374501</v>
+        <v>440530</v>
       </c>
       <c r="R71" t="n">
-        <v>7048627.665063544</v>
+        <v>7047514</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8690,22 +7940,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8714,34 +7959,28 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>97079295</v>
+        <v>128236789</v>
       </c>
       <c r="B72" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8749,40 +7988,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Gärdesån, Jmt</t>
+          <t>Gärde S, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440341.3908818047</v>
+        <v>440467</v>
       </c>
       <c r="R72" t="n">
-        <v>7047930.09822528</v>
+        <v>7047649</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8806,27 +8042,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8835,67 +8061,66 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128236786</v>
+        <v>90799380</v>
       </c>
       <c r="B73" t="n">
-        <v>57716</v>
+        <v>57141</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440548</v>
+        <v>440159</v>
       </c>
       <c r="R73" t="n">
-        <v>7047339</v>
+        <v>7048144</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8919,17 +8144,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Synobs av tjäder</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8940,64 +8165,73 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128236784</v>
+        <v>91131389</v>
       </c>
       <c r="B74" t="n">
-        <v>57716</v>
+        <v>99017</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>219795</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440471</v>
+        <v>440284</v>
       </c>
       <c r="R74" t="n">
-        <v>7047318</v>
+        <v>7047388</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9021,17 +8255,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9042,64 +8271,78 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128236817</v>
+        <v>91131398</v>
       </c>
       <c r="B75" t="n">
-        <v>79120</v>
+        <v>99456</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440606</v>
+        <v>440465</v>
       </c>
       <c r="R75" t="n">
-        <v>7047293</v>
+        <v>7047361</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9123,17 +8366,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9144,64 +8382,78 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128236814</v>
+        <v>91131382</v>
       </c>
       <c r="B76" t="n">
-        <v>91522</v>
+        <v>104628</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>222412</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440566</v>
+        <v>440284</v>
       </c>
       <c r="R76" t="n">
-        <v>7047307</v>
+        <v>7047388</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9225,12 +8477,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9241,64 +8493,78 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128236789</v>
+        <v>91131396</v>
       </c>
       <c r="B77" t="n">
-        <v>57716</v>
+        <v>104628</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>222412</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440467</v>
+        <v>440465</v>
       </c>
       <c r="R77" t="n">
-        <v>7047649</v>
+        <v>7047361</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9322,17 +8588,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9343,64 +8604,78 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128236782</v>
+        <v>90799381</v>
       </c>
       <c r="B78" t="n">
-        <v>57716</v>
+        <v>101326</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440231</v>
+        <v>440159</v>
       </c>
       <c r="R78" t="n">
-        <v>7048069</v>
+        <v>7048144</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9424,17 +8699,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Synobs av tjäder</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9445,64 +8720,73 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128236785</v>
+        <v>91131390</v>
       </c>
       <c r="B79" t="n">
-        <v>57716</v>
+        <v>101326</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440476</v>
+        <v>440284</v>
       </c>
       <c r="R79" t="n">
-        <v>7047442</v>
+        <v>7047388</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9526,17 +8810,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9547,64 +8826,78 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128236813</v>
+        <v>91131401</v>
       </c>
       <c r="B80" t="n">
-        <v>91522</v>
+        <v>101326</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>440489</v>
+        <v>440465</v>
       </c>
       <c r="R80" t="n">
-        <v>7047346</v>
+        <v>7047361</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9628,12 +8921,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9644,64 +8937,78 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128236788</v>
+        <v>90799460</v>
       </c>
       <c r="B81" t="n">
-        <v>57716</v>
+        <v>80392</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Gärde S, Jmt</t>
+          <t>Gärde-Tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440530</v>
+        <v>440422</v>
       </c>
       <c r="R81" t="n">
-        <v>7047514</v>
+        <v>7047763</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9725,17 +9032,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9746,19 +9053,38 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Äldre sälg</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38791-2025 artfynd.xlsx
+++ b/artfynd/A 38791-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY81"/>
+  <dimension ref="A1:AZ81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236809</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236811</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97079531</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236780</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236820</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236819</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236779</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97079078</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1557,6 +1602,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97079538</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1658,6 +1708,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97079058</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97079535</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1875,6 +1935,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90799374</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1977,6 +2042,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236793</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2079,6 +2149,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236794</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2181,6 +2256,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236795</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2283,6 +2363,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236796</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2385,6 +2470,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236797</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2487,6 +2577,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236798</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2589,6 +2684,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236799</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2691,6 +2791,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236800</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2792,6 +2897,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131267</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2898,6 +3008,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131372</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3009,6 +3124,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131313</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3115,6 +3235,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131365</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3226,6 +3351,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131308</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3337,6 +3467,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131314</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3434,6 +3569,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236803</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3540,6 +3680,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131370</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3641,6 +3786,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131268</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3752,6 +3902,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131309</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3863,6 +4018,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131311</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3974,6 +4134,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131315</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4078,6 +4243,11 @@
       <c r="AY34" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131373</t>
         </is>
       </c>
     </row>
@@ -4182,6 +4352,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97079546</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4289,6 +4464,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90799376</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4386,6 +4566,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236805</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4483,6 +4668,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236806</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4580,6 +4770,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236808</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4677,6 +4872,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236810</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4778,6 +4978,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97079510</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4879,6 +5084,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97079525</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4981,6 +5191,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236783</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5083,6 +5298,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236790</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5185,6 +5405,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236791</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5287,6 +5512,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236792</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5393,6 +5623,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131356</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5509,6 +5744,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90799475</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5606,6 +5846,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236781</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5707,6 +5952,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97079043</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5808,6 +6058,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97079052</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5914,6 +6169,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97079295</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6016,6 +6276,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236817</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6127,6 +6392,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90799389</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6248,6 +6518,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90799458</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6362,6 +6637,11 @@
       <c r="AY56" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90799473</t>
         </is>
       </c>
     </row>
@@ -6465,6 +6745,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97079293</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6576,6 +6861,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90799390</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6692,6 +6982,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90799470</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6803,6 +7098,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90799394</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6912,6 +7212,11 @@
       <c r="AY61" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90799392</t>
         </is>
       </c>
     </row>
@@ -7020,6 +7325,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97079272</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7122,6 +7432,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236782</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7224,6 +7539,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236784</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7326,6 +7646,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236785</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7428,6 +7753,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236786</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7530,6 +7860,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236788</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7632,6 +7967,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128236789</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7743,6 +8083,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90799380</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7854,6 +8199,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131389</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7965,6 +8315,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131398</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8076,6 +8431,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131407</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8187,6 +8547,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131405</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8298,6 +8663,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131382</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8409,6 +8779,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131396</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8520,6 +8895,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90799381</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8631,6 +9011,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90799468</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8742,6 +9127,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131390</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8853,6 +9243,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131401</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8964,6 +9359,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91131408</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9085,8 +9485,95 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90799460</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>